--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486954_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486954_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.195399999999999</v>
+        <v>7.7088</v>
       </c>
       <c r="E2" t="n">
-        <v>6.1878</v>
+        <v>5.2348</v>
       </c>
       <c r="F2" t="n">
-        <v>3.0076</v>
+        <v>2.474</v>
       </c>
       <c r="G2" t="n">
         <v>4.1032</v>
@@ -610,13 +610,13 @@
         <v>2.4641</v>
       </c>
       <c r="S2" t="n">
-        <v>2.8253</v>
+        <v>1.3387</v>
       </c>
       <c r="T2" t="n">
-        <v>2.4483</v>
+        <v>1.4952</v>
       </c>
       <c r="U2" t="n">
-        <v>0.377</v>
+        <v>-0.1566</v>
       </c>
       <c r="V2" t="n">
         <v>0.8295</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.1409</v>
+        <v>5.4013</v>
       </c>
       <c r="E3" t="n">
-        <v>2.6141</v>
+        <v>2.0524</v>
       </c>
       <c r="F3" t="n">
-        <v>3.5268</v>
+        <v>3.3489</v>
       </c>
       <c r="G3" t="n">
         <v>3.4097</v>
@@ -688,13 +688,13 @@
         <v>2.6694</v>
       </c>
       <c r="S3" t="n">
-        <v>1.222</v>
+        <v>0.4824</v>
       </c>
       <c r="T3" t="n">
-        <v>1.2512</v>
+        <v>0.6894</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0291</v>
+        <v>-0.207</v>
       </c>
       <c r="V3" t="n">
         <v>2.9466</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.3694</v>
+        <v>3.7729</v>
       </c>
       <c r="E4" t="n">
-        <v>1.1459</v>
+        <v>2.4012</v>
       </c>
       <c r="F4" t="n">
-        <v>1.2235</v>
+        <v>1.3717</v>
       </c>
       <c r="G4" t="n">
         <v>3.7225</v>
@@ -766,13 +766,13 @@
         <v>2.2588</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.1642</v>
+        <v>0.2393</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6433</v>
+        <v>0.612</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.5209</v>
+        <v>-0.3727</v>
       </c>
       <c r="V4" t="n">
         <v>1.6591</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9957</v>
+        <v>2.4256</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.3456</v>
+        <v>-0.0047</v>
       </c>
       <c r="F5" t="n">
-        <v>2.3413</v>
+        <v>2.4303</v>
       </c>
       <c r="G5" t="n">
         <v>-0.0171</v>
@@ -844,13 +844,13 @@
         <v>2.2588</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.6381</v>
+        <v>-0.2082</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1509</v>
+        <v>0.4918</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.7889</v>
+        <v>-0.7</v>
       </c>
       <c r="V5" t="n">
         <v>1.4189</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0582</v>
+        <v>0.1332</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1915</v>
+        <v>-0.08690000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2497</v>
+        <v>0.22</v>
       </c>
       <c r="G6" t="n">
         <v>0.5041</v>
@@ -922,13 +922,13 @@
         <v>0.4107</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.8566</v>
+        <v>-0.7816</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3294</v>
+        <v>-0.2248</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5272</v>
+        <v>-0.5569</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.2258</v>
+        <v>-1.0916</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.895</v>
+        <v>-0.7904</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3308</v>
+        <v>-0.3012</v>
       </c>
       <c r="G8" t="n">
         <v>-0.8077</v>
@@ -1078,13 +1078,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1779</v>
+        <v>-0.0436</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1976</v>
+        <v>-0.093</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0198</v>
+        <v>0.0494</v>
       </c>
       <c r="V8" t="n">
         <v>-0.2402</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.871</v>
+        <v>-1.8364</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.4342</v>
+        <v>-1.5775</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4368</v>
+        <v>-0.2589</v>
       </c>
       <c r="G9" t="n">
         <v>-2.0437</v>
@@ -1156,13 +1156,13 @@
         <v>0.4107</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0023</v>
+        <v>0.0368</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4416</v>
+        <v>0.2983</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4393</v>
+        <v>-0.2615</v>
       </c>
       <c r="V9" t="n">
         <v>-0.2402</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>N. ZIZIC</t>
+          <t>K. JOHNSON</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.5193</v>
+        <v>-2.0289</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.4087</v>
+        <v>-5.3078</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1107</v>
+        <v>3.2789</v>
       </c>
       <c r="G10" t="n">
-        <v>-4.6758</v>
+        <v>-1.0837</v>
       </c>
       <c r="H10" t="n">
-        <v>-5.0179</v>
+        <v>-1.6285</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3422</v>
+        <v>0.5448</v>
       </c>
       <c r="J10" t="n">
-        <v>-4.842</v>
+        <v>-3.0346</v>
       </c>
       <c r="K10" t="n">
-        <v>-4.8815</v>
+        <v>-2.4161</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0395</v>
+        <v>-0.6183999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1662</v>
+        <v>1.9509</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1365</v>
+        <v>0.7876</v>
       </c>
       <c r="O10" t="n">
-        <v>0.3027</v>
+        <v>1.1633</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>-2.4641</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-4.1068</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.6427</v>
       </c>
       <c r="S10" t="n">
-        <v>1.1564</v>
+        <v>-0.9472</v>
       </c>
       <c r="T10" t="n">
-        <v>1.4333</v>
+        <v>0.06569999999999999</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2769</v>
+        <v>-1.0129</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>2.4661</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.7679</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>0.6982</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>K. JOHNSON</t>
+          <t>G. BLAT BAEZA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.5689</v>
+        <v>-3.1663</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.5514</v>
+        <v>-2.3923</v>
       </c>
       <c r="F11" t="n">
-        <v>2.9825</v>
+        <v>-0.7739</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.0837</v>
+        <v>-1.1196</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.6285</v>
+        <v>-1.3433</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5448</v>
+        <v>0.2238</v>
       </c>
       <c r="J11" t="n">
-        <v>-3.0346</v>
+        <v>-0.5286</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.4161</v>
+        <v>-0.5416</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.6183999999999999</v>
+        <v>0.013</v>
       </c>
       <c r="M11" t="n">
-        <v>1.9509</v>
+        <v>-0.591</v>
       </c>
       <c r="N11" t="n">
-        <v>0.7876</v>
+        <v>-0.8017</v>
       </c>
       <c r="O11" t="n">
-        <v>1.1633</v>
+        <v>0.2107</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.4641</v>
+        <v>-1.0267</v>
       </c>
       <c r="Q11" t="n">
-        <v>-4.1068</v>
+        <v>-2.0534</v>
       </c>
       <c r="R11" t="n">
-        <v>1.6427</v>
+        <v>1.0267</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.4873</v>
+        <v>-0.2993</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.178</v>
+        <v>0.1897</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.3093</v>
+        <v>-0.489</v>
       </c>
       <c r="V11" t="n">
-        <v>2.4661</v>
+        <v>-0.7207</v>
       </c>
       <c r="W11" t="n">
-        <v>1.7679</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0.6982</v>
+        <v>-0.7207</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>G. BLAT BAEZA</t>
+          <t>N. ZIZIC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.7213</v>
+        <v>-4.4772</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.7991</v>
+        <v>-4.2183</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.9222</v>
+        <v>-0.2589</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.1196</v>
+        <v>-4.6758</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.3433</v>
+        <v>-5.0179</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2238</v>
+        <v>0.3422</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.5286</v>
+        <v>-4.842</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.5416</v>
+        <v>-4.8815</v>
       </c>
       <c r="L12" t="n">
-        <v>0.013</v>
+        <v>0.0395</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.591</v>
+        <v>0.1662</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.8017</v>
+        <v>-0.1365</v>
       </c>
       <c r="O12" t="n">
-        <v>0.2107</v>
+        <v>0.3027</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.0267</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.0534</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.0267</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.8542999999999999</v>
+        <v>0.1985</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2171</v>
+        <v>0.6237</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6372</v>
+        <v>-0.4251</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.7207</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.7207</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.501899999999999</v>
+        <v>6.489999999999998</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.8558</v>
+        <v>-4.867599999999999</v>
       </c>
       <c r="F13" t="n">
         <v>11.3576</v>
@@ -1444,10 +1444,10 @@
         <v>-0.2056999999999993</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.8879000000000002</v>
+        <v>-0.8879000000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>0.6820999999999999</v>
+        <v>0.6820999999999998</v>
       </c>
       <c r="M13" t="n">
         <v>1.7725</v>
@@ -1468,13 +1468,13 @@
         <v>13.3472</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.1041</v>
+        <v>-0.1159000000000002</v>
       </c>
       <c r="T13" t="n">
-        <v>2.9623</v>
+        <v>3.950400000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>-4.0661</v>
+        <v>-4.066399999999999</v>
       </c>
       <c r="V13" t="n">
         <v>8.1191</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. SANTANO BARTOLOME</t>
+          <t>J. PUIDET</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.4782</v>
+        <v>3.8488</v>
       </c>
       <c r="E14" t="n">
-        <v>4.7593</v>
+        <v>0.8483000000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.2811</v>
+        <v>3.0005</v>
       </c>
       <c r="G14" t="n">
-        <v>1.3563</v>
+        <v>1.4576</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0064</v>
+        <v>1.6706</v>
       </c>
       <c r="I14" t="n">
-        <v>1.3499</v>
+        <v>-0.213</v>
       </c>
       <c r="J14" t="n">
-        <v>1.5817</v>
+        <v>1.4723</v>
       </c>
       <c r="K14" t="n">
-        <v>0.2794</v>
+        <v>1.5252</v>
       </c>
       <c r="L14" t="n">
-        <v>1.3024</v>
+        <v>-0.0529</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.2254</v>
+        <v>-0.0147</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.2729</v>
+        <v>0.1455</v>
       </c>
       <c r="O14" t="n">
-        <v>0.0475</v>
+        <v>-0.1602</v>
       </c>
       <c r="P14" t="n">
-        <v>1.2321</v>
+        <v>1.0267</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-1.4374</v>
       </c>
       <c r="R14" t="n">
-        <v>1.2321</v>
+        <v>2.4641</v>
       </c>
       <c r="S14" t="n">
-        <v>1.1916</v>
+        <v>1.1468</v>
       </c>
       <c r="T14" t="n">
-        <v>1.9989</v>
+        <v>0.8133</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.8073</v>
+        <v>0.3334</v>
       </c>
       <c r="V14" t="n">
-        <v>0.6982</v>
+        <v>0.2177</v>
       </c>
       <c r="W14" t="n">
-        <v>1.1786</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.4805</v>
+        <v>0.2177</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. PUIDET</t>
+          <t>J. SANTANO BARTOLOME</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.1208</v>
+        <v>3.4356</v>
       </c>
       <c r="E15" t="n">
-        <v>1.1621</v>
+        <v>3.3995</v>
       </c>
       <c r="F15" t="n">
-        <v>2.9587</v>
+        <v>0.0362</v>
       </c>
       <c r="G15" t="n">
-        <v>1.4576</v>
+        <v>1.3563</v>
       </c>
       <c r="H15" t="n">
-        <v>1.6706</v>
+        <v>0.0064</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.213</v>
+        <v>1.3499</v>
       </c>
       <c r="J15" t="n">
-        <v>1.4723</v>
+        <v>1.5817</v>
       </c>
       <c r="K15" t="n">
-        <v>1.5252</v>
+        <v>0.2794</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.0529</v>
+        <v>1.3024</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.0147</v>
+        <v>-0.2254</v>
       </c>
       <c r="N15" t="n">
-        <v>0.1455</v>
+        <v>-0.2729</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.1602</v>
+        <v>0.0475</v>
       </c>
       <c r="P15" t="n">
-        <v>1.0267</v>
+        <v>1.2321</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.4374</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.4641</v>
+        <v>1.2321</v>
       </c>
       <c r="S15" t="n">
-        <v>1.4188</v>
+        <v>0.1491</v>
       </c>
       <c r="T15" t="n">
-        <v>1.1272</v>
+        <v>0.6391</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2916</v>
+        <v>-0.49</v>
       </c>
       <c r="V15" t="n">
-        <v>0.2177</v>
+        <v>0.6982</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.1786</v>
       </c>
       <c r="X15" t="n">
-        <v>0.2177</v>
+        <v>-0.4805</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. ECHEVERRIA FERNANDEZ</t>
+          <t>D. SIMEUNOVIC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4623</v>
+        <v>0.7875</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.5681</v>
+        <v>-0.5548999999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>1.0304</v>
+        <v>1.3423</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.8346</v>
+        <v>1.1251</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.6664</v>
+        <v>2.5015</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1682</v>
+        <v>-1.3763</v>
       </c>
       <c r="J16" t="n">
-        <v>-2.5747</v>
+        <v>1.1974</v>
       </c>
       <c r="K16" t="n">
-        <v>-2.6142</v>
+        <v>2.1583</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0395</v>
+        <v>-0.9609</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.2599</v>
+        <v>-0.0722</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.0522</v>
+        <v>0.3431</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.2077</v>
+        <v>-0.4154</v>
       </c>
       <c r="P16" t="n">
-        <v>1.4374</v>
+        <v>0.616</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.4107</v>
+        <v>-2.2588</v>
       </c>
       <c r="R16" t="n">
-        <v>1.8481</v>
+        <v>2.8748</v>
       </c>
       <c r="S16" t="n">
-        <v>2.0998</v>
+        <v>0.2024</v>
       </c>
       <c r="T16" t="n">
-        <v>2.4174</v>
+        <v>0.484</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3176</v>
+        <v>-0.2816</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.2402</v>
+        <v>-1.1561</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>0.0225</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2402</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. SIMEUNOVIC</t>
+          <t>E. MEDINA ROA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0825</v>
+        <v>0.1346</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.0779</v>
+        <v>-0.8927</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9954</v>
+        <v>1.0273</v>
       </c>
       <c r="G17" t="n">
-        <v>1.1251</v>
+        <v>0.5327</v>
       </c>
       <c r="H17" t="n">
-        <v>2.5015</v>
+        <v>1.427</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.3763</v>
+        <v>-0.8943</v>
       </c>
       <c r="J17" t="n">
-        <v>1.1974</v>
+        <v>1.1919</v>
       </c>
       <c r="K17" t="n">
-        <v>2.1583</v>
+        <v>1.113</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.9609</v>
+        <v>0.0789</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.0722</v>
+        <v>-0.6592</v>
       </c>
       <c r="N17" t="n">
-        <v>0.3431</v>
+        <v>0.314</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.4154</v>
+        <v>-0.9732</v>
       </c>
       <c r="P17" t="n">
-        <v>0.616</v>
+        <v>-0.2053</v>
       </c>
       <c r="Q17" t="n">
         <v>-2.2588</v>
       </c>
       <c r="R17" t="n">
-        <v>2.8748</v>
+        <v>2.0534</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6676</v>
+        <v>0.0475</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.039</v>
+        <v>0.1741</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.6286</v>
+        <v>-0.1267</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.1561</v>
+        <v>-0.2402</v>
       </c>
       <c r="W17" t="n">
-        <v>0.0225</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.1786</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>E. MEDINA ROA</t>
+          <t>M. ECHEVERRIA FERNANDEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.6168</v>
+        <v>-0.5488</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.4157</v>
+        <v>-1.7187</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7989000000000001</v>
+        <v>1.1699</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5327</v>
+        <v>-2.8346</v>
       </c>
       <c r="H18" t="n">
-        <v>1.427</v>
+        <v>-2.6664</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.8943</v>
+        <v>-0.1682</v>
       </c>
       <c r="J18" t="n">
-        <v>1.1919</v>
+        <v>-2.5747</v>
       </c>
       <c r="K18" t="n">
-        <v>1.113</v>
+        <v>-2.6142</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0789</v>
+        <v>0.0395</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.6592</v>
+        <v>-0.2599</v>
       </c>
       <c r="N18" t="n">
-        <v>0.314</v>
+        <v>-0.0522</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.9732</v>
+        <v>-0.2077</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.2053</v>
+        <v>1.4374</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.2588</v>
+        <v>-0.4107</v>
       </c>
       <c r="R18" t="n">
-        <v>2.0534</v>
+        <v>1.8481</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.7039</v>
+        <v>1.0886</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3489</v>
+        <v>1.2667</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3551</v>
+        <v>-0.1781</v>
       </c>
       <c r="V18" t="n">
         <v>-0.2402</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.4972</v>
+        <v>-1.7744</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.4289</v>
+        <v>-1.6381</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.0683</v>
+        <v>-0.1363</v>
       </c>
       <c r="G19" t="n">
         <v>-0.1066</v>
@@ -1936,13 +1936,13 @@
         <v>0.4107</v>
       </c>
       <c r="S19" t="n">
-        <v>0.6094000000000001</v>
+        <v>0.3322</v>
       </c>
       <c r="T19" t="n">
-        <v>0.4416</v>
+        <v>0.2324</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1678</v>
+        <v>0.0998</v>
       </c>
       <c r="V19" t="n">
         <v>-1.1786</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.0614</v>
+        <v>-1.9892</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.394</v>
+        <v>-2.4526</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3327</v>
+        <v>0.4634</v>
       </c>
       <c r="G20" t="n">
         <v>1.4135</v>
@@ -2014,13 +2014,13 @@
         <v>2.2588</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.2223</v>
+        <v>-0.1501</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7364000000000001</v>
+        <v>0.205</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4859</v>
+        <v>-0.3552</v>
       </c>
       <c r="V20" t="n">
         <v>-2.2259</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.4324</v>
+        <v>-3.0872</v>
       </c>
       <c r="E21" t="n">
-        <v>-5.3245</v>
+        <v>-4.8015</v>
       </c>
       <c r="F21" t="n">
-        <v>1.8921</v>
+        <v>1.7143</v>
       </c>
       <c r="G21" t="n">
         <v>-1.8447</v>
@@ -2092,13 +2092,13 @@
         <v>1.8481</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4788</v>
+        <v>-0.1337</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5038</v>
+        <v>0.0192</v>
       </c>
       <c r="U21" t="n">
-        <v>0.025</v>
+        <v>-0.1529</v>
       </c>
       <c r="V21" t="n">
         <v>-0.6982</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.8728</v>
+        <v>-4.9139</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.0699</v>
+        <v>-3.5469</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.8029</v>
+        <v>-1.367</v>
       </c>
       <c r="G22" t="n">
         <v>-2.6662</v>
@@ -2170,13 +2170,13 @@
         <v>1.4374</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.143</v>
+        <v>-0.1841</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2907</v>
+        <v>0.2323</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.8522999999999999</v>
+        <v>-0.4164</v>
       </c>
       <c r="V22" t="n">
         <v>-3.2957</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.501800000000001</v>
+        <v>-4.107</v>
       </c>
       <c r="E23" t="n">
         <v>-11.3576</v>
       </c>
       <c r="F23" t="n">
-        <v>5.8559</v>
+        <v>7.250599999999999</v>
       </c>
       <c r="G23" t="n">
         <v>-1.5669</v>
@@ -2233,10 +2233,10 @@
         <v>0.2058</v>
       </c>
       <c r="N23" t="n">
-        <v>0.8878999999999999</v>
+        <v>0.8879000000000001</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.6821000000000002</v>
+        <v>-0.6820999999999999</v>
       </c>
       <c r="P23" t="n">
         <v>3.0802</v>
@@ -2248,13 +2248,13 @@
         <v>16.4275</v>
       </c>
       <c r="S23" t="n">
-        <v>1.104</v>
+        <v>2.4987</v>
       </c>
       <c r="T23" t="n">
-        <v>4.0663</v>
+        <v>4.0661</v>
       </c>
       <c r="U23" t="n">
-        <v>-2.9624</v>
+        <v>-1.5677</v>
       </c>
       <c r="V23" t="n">
         <v>-8.119</v>
